--- a/Excel/MazeConfig.xlsx
+++ b/Excel/MazeConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maze_nodes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maze_puzzles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maze_traps" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maze_fragments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maze_rules" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="maze_nodes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="maze_puzzles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="maze_traps" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="maze_fragments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="maze_rules" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -41,7 +41,13 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -64,74 +70,6 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -596,7 +534,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>{"correct_items":1,"wrong_items":1,"old_coin":1,"empty_bowl":1}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="J5" s="6" t="n">
@@ -718,7 +656,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"天枢": 1, "天璇": 1, "天玑": 1, "天权": 1, "玉衡": 1, "开阳": 1, "瑶光": 1}</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
@@ -1511,17 +1449,17 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>correct_items</t>
+          <t>天枢,天璇,天玑,天权,玉衡,开阳,瑶光</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>右侧显示关卡提示，放置房间内拾取的正确道具</t>
+          <t>一枢二璇三玑四权，五衡六阳七光</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>["correct_items","wrong_items","old_coin","empty_bowl"]</t>
+          <t>["天枢", "天璇", "天玑", "天权", "玉衡", "开阳", "瑶光"]</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
